--- a/plantillas/consulta/UTNo_Recibieron_Opiniones.xlsx
+++ b/plantillas/consulta/UTNo_Recibieron_Opiniones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD52AF8A-5CC6-4FF7-8FB6-B7ABA94E0E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED61EA0F-46F7-4646-935F-DF567791912A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -179,9 +179,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -498,53 +495,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
@@ -558,18 +555,19 @@
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J10" s="3"/>

--- a/plantillas/consulta/UTNo_Recibieron_Opiniones.xlsx
+++ b/plantillas/consulta/UTNo_Recibieron_Opiniones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED61EA0F-46F7-4646-935F-DF567791912A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F98D611-1655-4508-9BC5-8A14A1DD4103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <t>Clave de Proyecto Especifico</t>
   </si>
   <si>
-    <t>Destino</t>
+    <t>Destino de los recursos</t>
   </si>
 </sst>
 </file>

--- a/plantillas/consulta/UTNo_Recibieron_Opiniones.xlsx
+++ b/plantillas/consulta/UTNo_Recibieron_Opiniones.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F98D611-1655-4508-9BC5-8A14A1DD4103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
